--- a/06_Client_Upload/Connection/00_START_HERE/Connection_Library_Index.xlsx
+++ b/06_Client_Upload/Connection/00_START_HERE/Connection_Library_Index.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Auto-generated catalog of 153 artifacts. Static upload-ready copy of the ECS working framework (artifacts only). Start with the Execution Guide (role + phase).</t>
+          <t>Auto-generated catalog of 159 artifacts. Static upload-ready copy of the ECS working framework (artifacts only). Start with the Execution Guide (role + phase).</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Connection_Kickoff_Deck.pptx</t>
+          <t>Connection_Communication_Plan.docx</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Customer_Governance_Charter.docx</t>
+          <t>Connection_Document_Roadmap.docx</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -601,22 +601,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>01_Onboarding</t>
+          <t>01_Onboarding/Client_Facing</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Connection_Onboarding_Checklist.xlsx</t>
+          <t>Connection_Kickoff_Deck.pptx</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Client-facing</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>01_Onboarding/Internal_Team</t>
+          <t>01_Onboarding/Client_Facing</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Connection_Engagement_Delivery_Guidelines.docx</t>
+          <t>Customer_Governance_Charter.docx</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ECS internal</t>
+          <t>Client-facing</t>
         </is>
       </c>
     </row>
@@ -651,22 +651,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>01_Onboarding/Internal_Team</t>
+          <t>01_Onboarding</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Connection_Role_and_Accountability_QuickRef.docx</t>
+          <t>Connection_Onboarding_Checklist.xlsx</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>ECS internal</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Connection_Sprint_Operating_Kit.docx</t>
+          <t>Connection_Engagement_Delivery_Guidelines.docx</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Connection_Team_Onboarding_and_Vision.docx</t>
+          <t>Connection_Role_and_Accountability_QuickRef.docx</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Connection_Workshop_Facilitation_Guide.docx</t>
+          <t>Connection_Sprint_Operating_Kit.docx</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/CMDB_CSDM_Accelerator_Pack</t>
+          <t>01_Onboarding/Internal_Team</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>00_README_CMDB_CSDM_Pack.docx</t>
+          <t>Connection_Team_Onboarding_and_Vision.docx</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Client (data)</t>
+          <t>ECS internal</t>
         </is>
       </c>
     </row>
@@ -776,22 +776,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/CMDB_CSDM_Accelerator_Pack</t>
+          <t>01_Onboarding/Internal_Team</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>01_csdm_service_taxonomy.xlsx</t>
+          <t>Connection_Workshop_Facilitation_Guide.docx</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Client (data)</t>
+          <t>ECS internal</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>02_ci_class_selection.xlsx</t>
+          <t>00_README_CMDB_CSDM_Pack.docx</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>03_business_service_definitions.xlsx</t>
+          <t>01_csdm_service_taxonomy.xlsx</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>04_technical_services_and_apps.xlsx</t>
+          <t>02_ci_class_selection.xlsx</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>05_service_ci_relationships.xlsx</t>
+          <t>03_business_service_definitions.xlsx</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>06_cmdb_governance_baseline.xlsx</t>
+          <t>04_technical_services_and_apps.xlsx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Discovery_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/CMDB_CSDM_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>00_README_Discovery_Pack.docx</t>
+          <t>05_service_ci_relationships.xlsx</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Discovery_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/CMDB_CSDM_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>01_discovery_scope.xlsx</t>
+          <t>06_cmdb_governance_baseline.xlsx</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>02_mid_server_config.xlsx</t>
+          <t>00_README_Discovery_Pack.docx</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>03_credential_management.xlsx</t>
+          <t>01_discovery_scope.xlsx</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>04_discovery_schedules.xlsx</t>
+          <t>02_mid_server_config.xlsx</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>05_sgc_configuration.xlsx</t>
+          <t>03_credential_management.xlsx</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>06_ire_reconciliation.xlsx</t>
+          <t>04_discovery_schedules.xlsx</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1101,17 +1101,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Employee_Center_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Discovery_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>00_README_Employee_Center_Pack.docx</t>
+          <t>05_sgc_configuration.xlsx</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Employee_Center_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Discovery_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>01_ec_portal_design.xlsx</t>
+          <t>06_ire_reconciliation.xlsx</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>02_topic_taxonomy.xlsx</t>
+          <t>00_README_Employee_Center_Pack.docx</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>03_homepage_layout.xlsx</t>
+          <t>01_ec_portal_design.xlsx</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>04_search_configuration.xlsx</t>
+          <t>02_topic_taxonomy.xlsx</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>05_adoption_measurement.xlsx</t>
+          <t>03_homepage_layout.xlsx</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Foundation_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Employee_Center_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>00_README_Foundation_Data_Pack.docx</t>
+          <t>04_search_configuration.xlsx</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Foundation_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Employee_Center_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>01_users.xlsx</t>
+          <t>05_adoption_measurement.xlsx</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>02_locations.xlsx</t>
+          <t>00_README_Foundation_Data_Pack.docx</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>03_departments.xlsx</t>
+          <t>01_users.xlsx</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>04_groups.xlsx</t>
+          <t>02_locations.xlsx</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>05_group_members.xlsx</t>
+          <t>03_departments.xlsx</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>06_assignment_rules.xlsx</t>
+          <t>04_groups.xlsx</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>07_schedules.xlsx</t>
+          <t>05_group_members.xlsx</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>08_slas.xlsx</t>
+          <t>06_assignment_rules.xlsx</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/ITAM_HAM_Foundations_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Foundation_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>00_README_HAM_Foundations_Pack.docx</t>
+          <t>07_schedules.xlsx</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/ITAM_HAM_Foundations_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Foundation_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>01_stockrooms.xlsx</t>
+          <t>08_slas.xlsx</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>02_asset_classes_baseline.xlsx</t>
+          <t>00_README_HAM_Foundations_Pack.docx</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>03_asset_models.xlsx</t>
+          <t>01_stockrooms.xlsx</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>04_initial_inventory.xlsx</t>
+          <t>02_asset_classes_baseline.xlsx</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>05_lifecycle_states_baseline.xlsx</t>
+          <t>03_asset_models.xlsx</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>06_assignment_and_receiving.xlsx</t>
+          <t>04_initial_inventory.xlsx</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/ITSM_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/ITAM_HAM_Foundations_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>00_README_ITSM_Process_Pack.docx</t>
+          <t>05_lifecycle_states_baseline.xlsx</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/ITSM_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/ITAM_HAM_Foundations_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>01_incident_management.xlsx</t>
+          <t>06_assignment_and_receiving.xlsx</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>02_major_incident_management.xlsx</t>
+          <t>00_README_ITSM_Process_Pack.docx</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>03_problem_management.xlsx</t>
+          <t>01_incident_management.xlsx</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>04_change_management.xlsx</t>
+          <t>02_major_incident_management.xlsx</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>05_service_request_management.xlsx</t>
+          <t>03_problem_management.xlsx</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>06_knowledge_management.xlsx</t>
+          <t>04_change_management.xlsx</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Integration_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/ITSM_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>00_README_Integration_Pack.docx</t>
+          <t>05_service_request_management.xlsx</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Integration_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/ITSM_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>01_active_directory.xlsx</t>
+          <t>06_knowledge_management.xlsx</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>02_single_sign_on.xlsx</t>
+          <t>00_README_Integration_Pack.docx</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>03_sccm.xlsx</t>
+          <t>01_active_directory.xlsx</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>04_intune.xlsx</t>
+          <t>02_single_sign_on.xlsx</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>05_vonage_cti_interactions.xlsx</t>
+          <t>03_sccm.xlsx</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Knowledge_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Integration_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>00_README_Knowledge_Pack.docx</t>
+          <t>04_intune.xlsx</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Knowledge_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Integration_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>01_kb_structure.xlsx</t>
+          <t>05_vonage_cti_interactions.xlsx</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>02_article_template_standards.xlsx</t>
+          <t>00_README_Knowledge_Pack.docx</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>03_access_controls.xlsx</t>
+          <t>01_kb_structure.xlsx</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>04_article_workflow.xlsx</t>
+          <t>02_article_template_standards.xlsx</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>05_search_optimization.xlsx</t>
+          <t>03_access_controls.xlsx</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>06_knowledge_kpis.xlsx</t>
+          <t>04_article_workflow.xlsx</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Performance_Analytics_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Knowledge_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>00_README_Performance_Analytics_Pack.docx</t>
+          <t>05_search_optimization.xlsx</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Performance_Analytics_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Knowledge_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>01_pa_scope_dashboard_inventory.xlsx</t>
+          <t>06_knowledge_kpis.xlsx</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>02_ootb_indicator_library.xlsx</t>
+          <t>00_README_Performance_Analytics_Pack.docx</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>03_dashboard_design.xlsx</t>
+          <t>01_pa_scope_dashboard_inventory.xlsx</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>04_scorecard_configuration.xlsx</t>
+          <t>02_ootb_indicator_library.xlsx</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>05_pa_governance.xlsx</t>
+          <t>03_dashboard_design.xlsx</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Predictive_Intelligence_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Performance_Analytics_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>00_README_Predictive_Intelligence_Pack.docx</t>
+          <t>04_scorecard_configuration.xlsx</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Predictive_Intelligence_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Performance_Analytics_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>01_pi_scope_readiness.xlsx</t>
+          <t>05_pa_governance.xlsx</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>02_category_classification.xlsx</t>
+          <t>00_README_Predictive_Intelligence_Pack.docx</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>03_similar_incident.xlsx</t>
+          <t>01_pi_scope_readiness.xlsx</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>04_assignment_intelligence.xlsx</t>
+          <t>02_category_classification.xlsx</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>05_pi_kpis.xlsx</t>
+          <t>03_similar_incident.xlsx</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Service_Catalog_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Predictive_Intelligence_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>00_README_Service_Catalog_Pack.docx</t>
+          <t>04_assignment_intelligence.xlsx</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Service_Catalog_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Predictive_Intelligence_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>01_category_rationalization.xlsx</t>
+          <t>05_pi_kpis.xlsx</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>02_catalog_item_inventory.xlsx</t>
+          <t>00_README_Service_Catalog_Pack.docx</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>03_item_template_standards.xlsx</t>
+          <t>01_category_rationalization.xlsx</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>04_fulfillment_workflow_decisions.xlsx</t>
+          <t>02_catalog_item_inventory.xlsx</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>05_approval_matrix.xlsx</t>
+          <t>03_item_template_standards.xlsx</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>06_catalog_item_config_data.xlsx</t>
+          <t>04_fulfillment_workflow_decisions.xlsx</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Virtual_Agent_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Service_Catalog_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>00_README_Virtual_Agent_Pack.docx</t>
+          <t>05_approval_matrix.xlsx</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Accelerator_Packs/Virtual_Agent_Accelerator_Pack</t>
+          <t>02_Delivery/Accelerator_Packs/Service_Catalog_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>01_va_scope_channel.xlsx</t>
+          <t>06_catalog_item_config_data.xlsx</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>02_topic_design_nlu.xlsx</t>
+          <t>00_README_Virtual_Agent_Pack.docx</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>03_handoff_escalation.xlsx</t>
+          <t>01_va_scope_channel.xlsx</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>04_va_analytics.xlsx</t>
+          <t>02_topic_design_nlu.xlsx</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>05_golive_readiness.xlsx</t>
+          <t>03_handoff_escalation.xlsx</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery</t>
+          <t>02_Delivery/Accelerator_Packs/Virtual_Agent_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Connection_18Week_Project_Plan.xlsx</t>
+          <t>04_va_analytics.xlsx</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Delivery / Both</t>
+          <t>Client (data)</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery</t>
+          <t>02_Delivery/Accelerator_Packs/Virtual_Agent_Accelerator_Pack</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Connection_Customer_Dependency_Tracker.xlsx</t>
+          <t>05_golive_readiness.xlsx</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Delivery / Both</t>
+          <t>Client (data)</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Connection_Cutover_Runbook.docx</t>
+          <t>Connection_18Week_Project_Plan.xlsx</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Connection_Delivery_Readiness_Audit.xlsx</t>
+          <t>Connection_Customer_Dependency_Tracker.xlsx</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Connection_Executive_Health_Dashboard.pptx</t>
+          <t>Connection_Cutover_Runbook.docx</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Connection_Go_Live_Readiness_Checklist.xlsx</t>
+          <t>Connection_Delivery_Readiness_Audit.xlsx</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Connection_Governance_Triage_and_RAID.xlsx</t>
+          <t>Connection_Executive_Health_Dashboard.pptx</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Connection_Operational_Handoff_Pack.docx</t>
+          <t>Connection_Go_Live_Readiness_Checklist.xlsx</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Connection_Platform_Architecture_and_CSDM_Alignment.docx</t>
+          <t>Connection_Governance_Triage_and_RAID.xlsx</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Connection_Project_Controls.xlsx</t>
+          <t>Connection_Operational_Handoff_Pack.docx</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Connection_Project_Delivery_Stories.xlsx</t>
+          <t>Connection_Platform_Architecture_and_CSDM_Alignment.docx</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Connection_RACI_Matrix.xlsx</t>
+          <t>Connection_Project_Controls.xlsx</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Connection_SIT_Test_Scripts.xlsx</t>
+          <t>Connection_Project_Delivery_Stories.xlsx</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Connection_SOW_Deliverables_Matrix.xlsx</t>
+          <t>Connection_RACI_Matrix.xlsx</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Connection_Sprint_Demo_TEMPLATE.pptx</t>
+          <t>Connection_SIT_Test_Scripts.xlsx</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Connection_Sprint_Plan_and_Capacity.xlsx</t>
+          <t>Connection_SOW_Deliverables_Matrix.xlsx</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Connection_UAT_End_to_End_Test_Scripts.xlsx</t>
+          <t>Connection_Sprint_Demo_TEMPLATE.pptx</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Connection_UAT_Guidebook_for_End_Users.docx</t>
+          <t>Connection_Sprint_Plan_and_Capacity.xlsx</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Connection_User_Stories_SN_Agile.xlsx</t>
+          <t>Connection_UAT_End_to_End_Test_Scripts.xlsx</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Connection_Weekly_Status_Report_TEMPLATE.docx</t>
+          <t>Connection_UAT_Guidebook_for_End_Users.docx</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -3276,22 +3276,22 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Knowledge_Transfer</t>
+          <t>02_Delivery</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Connection_Administrator_Guide_and_KT.docx</t>
+          <t>Connection_User_Stories_SN_Agile.xlsx</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Client-facing (KT)</t>
+          <t>Delivery / Both</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Knowledge_Transfer</t>
+          <t>02_Delivery</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Connection_Train_the_Trainer_Toolkit.docx</t>
+          <t>Connection_Weekly_Status_Report_TEMPLATE.docx</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Client-facing (KT)</t>
+          <t>Delivery / Both</t>
         </is>
       </c>
     </row>
@@ -3326,22 +3326,22 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops</t>
+          <t>02_Delivery/Knowledge_Transfer</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Connection_CMDB_Workshop.pptx</t>
+          <t>Connection_Administrator_Guide_and_KT.docx</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Client-facing</t>
+          <t>Client-facing (KT)</t>
         </is>
       </c>
     </row>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops</t>
+          <t>02_Delivery/Knowledge_Transfer</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Connection_CSDM_Workshop.pptx</t>
+          <t>Connection_Train_the_Trainer_Toolkit.docx</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Client-facing</t>
+          <t>Client-facing (KT)</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Connection_Change_Workshop.pptx</t>
+          <t>Connection_CMDB_Workshop.pptx</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Connection_Discovery_Workshop.pptx</t>
+          <t>Connection_CSDM_Workshop.pptx</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Connection_Employee_Center_Workshop.pptx</t>
+          <t>Connection_Change_Workshop.pptx</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Connection_HAM_Workshop.pptx</t>
+          <t>Connection_Discovery_Workshop.pptx</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Connection_Incident_Workshop.pptx</t>
+          <t>Connection_Employee_Center_Workshop.pptx</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Connection_Integrations_Workshop.pptx</t>
+          <t>Connection_HAM_Workshop.pptx</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Connection_Interactions_Vonage_CTI_Workshop.pptx</t>
+          <t>Connection_Incident_Workshop.pptx</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Connection_Knowledge_Workshop.pptx</t>
+          <t>Connection_Integrations_Workshop.pptx</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Connection_Major_Incident_Workshop.pptx</t>
+          <t>Connection_Interactions_Vonage_CTI_Workshop.pptx</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Connection_Performance_Analytics_Workshop.pptx</t>
+          <t>Connection_Knowledge_Workshop.pptx</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Connection_Platform_Foundation_Workshop.pptx</t>
+          <t>Connection_Major_Incident_Workshop.pptx</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Connection_Predictive_Intelligence_Workshop.pptx</t>
+          <t>Connection_Performance_Analytics_Workshop.pptx</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Connection_Problem_Workshop.pptx</t>
+          <t>Connection_Platform_Foundation_Workshop.pptx</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Connection_Service_Catalog_Workshop.pptx</t>
+          <t>Connection_Predictive_Intelligence_Workshop.pptx</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Connection_Service_Graph_Connectors_Workshop.pptx</t>
+          <t>Connection_Problem_Workshop.pptx</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Connection_Virtual_Agent_Workshop.pptx</t>
+          <t>Connection_Service_Catalog_Workshop.pptx</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Connection_Workshop_Scope_Notes.docx</t>
+          <t>Connection_Service_Graph_Connectors_Workshop.pptx</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -3801,22 +3801,22 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops/Demo_Scripts</t>
+          <t>02_Delivery/Workshops</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-01_Incident_Management_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_Virtual_Agent_Workshop.pptx</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>ECS internal</t>
+          <t>Client-facing</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops/Demo_Scripts</t>
+          <t>02_Delivery/Workshops</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-02_Catalog_Request_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_Workshop_Scope_Notes.docx</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>ECS internal</t>
+          <t>Client-facing</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-03_Knowledge_VA_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_INT-DS-01_Incident_Management_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-04_Change_Management_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_INT-DS-02_Catalog_Request_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-05_CSDM_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_INT-DS-03_Knowledge_VA_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-06_HAM_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_INT-DS-04_Change_Management_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Connection_INT-DS-07_Performance_Analytics_Demo_Script_INTERNAL.docx</t>
+          <t>Connection_INT-DS-05_CSDM_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops/Pre_Reads</t>
+          <t>02_Delivery/Workshops/Demo_Scripts</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_01_Platform_Foundation_CLIENT.docx</t>
+          <t>Connection_INT-DS-06_HAM_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Client-facing</t>
+          <t>ECS internal</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>02_Delivery/Workshops/Pre_Reads</t>
+          <t>02_Delivery/Workshops/Demo_Scripts</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_02_Incident_Management_CLIENT.docx</t>
+          <t>Connection_INT-DS-07_Performance_Analytics_Demo_Script_INTERNAL.docx</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Client-facing</t>
+          <t>ECS internal</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_03_Major_Incident_Management_CLIENT.docx</t>
+          <t>Connection_WP_01_Platform_Foundation_CLIENT.docx</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_04_Problem_Management_CLIENT.docx</t>
+          <t>Connection_WP_02_Incident_Management_CLIENT.docx</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_05_Change_Management_CLIENT.docx</t>
+          <t>Connection_WP_03_Major_Incident_Management_CLIENT.docx</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_06_Service_Catalog_Request_CLIENT.docx</t>
+          <t>Connection_WP_04_Problem_Management_CLIENT.docx</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_07_Knowledge_Management_CLIENT.docx</t>
+          <t>Connection_WP_05_Change_Management_CLIENT.docx</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_08_Employee_Center_CLIENT.docx</t>
+          <t>Connection_WP_06_Service_Catalog_Request_CLIENT.docx</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_09_Virtual_Agent_CLIENT.docx</t>
+          <t>Connection_WP_07_Knowledge_Management_CLIENT.docx</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_10_Predictive_Intelligence_CLIENT.docx</t>
+          <t>Connection_WP_08_Employee_Center_CLIENT.docx</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_12_CSDM_CLIENT.docx</t>
+          <t>Connection_WP_09_Virtual_Agent_CLIENT.docx</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_13_CMDB_CLIENT.docx</t>
+          <t>Connection_WP_10_Predictive_Intelligence_CLIENT.docx</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Connection_WP_14_Discovery_CLIENT.docx</t>
+          <t>Connection_WP_12_CSDM_CLIENT.docx</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Connection_WP_15_Service_Graph_Connectors_CLIENT.docx</t>
+          <t>Connection_WP_13_CMDB_CLIENT.docx</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -4331,17 +4331,167 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
+          <t>Connection_WP_14_Discovery_CLIENT.docx</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>Client-facing</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>02_Delivery/Workshops/Pre_Reads</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Connection_WP_15_Service_Graph_Connectors_CLIENT.docx</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Client-facing</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>02_Delivery/Workshops/Pre_Reads</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
           <t>Connection_WP_16_Hardware_Asset_Management_CLIENT.docx</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
         <is>
           <t>Client-facing</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>(root)</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Connection_Native_Page_PASTE_Checklist.docx</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Delivery / Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>(root)</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Connection_Native_SharePoint_Page_Build_Guide.docx</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Delivery / Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>(root)</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Connection_SharePoint_Publish_and_Test_Runbook.docx</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Delivery / Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>(root)</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Connection_SharePoint_Publishing_Blueprint.docx</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Delivery / Both</t>
         </is>
       </c>
     </row>
